--- a/inventory_solution.xlsx
+++ b/inventory_solution.xlsx
@@ -5,10 +5,10 @@
   <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\OneDrive\Desktop\Excel_project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2405960-3890-4213-91F0-B9121179175F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{223FD9F7-01F6-42B9-A5B4-966C3355C1ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,9 +24,9 @@
     <definedName name="NativeTimeline_Last_Updated">#N/A</definedName>
     <definedName name="Slicer_Region">#N/A</definedName>
   </definedNames>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191028" iterate="1" iterateCount="1"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId6"/>
+    <pivotCache cacheId="1" r:id="rId6"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
@@ -2081,7 +2081,7 @@
     <t>AOV</t>
   </si>
   <si>
-    <t>Sales Dashboard</t>
+    <t>Inventory Sales Dashboard</t>
   </si>
 </sst>
 </file>
@@ -18045,7 +18045,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9BE36CEB-A123-4E3F-9601-73D921FA7399}" name="PivotTable5" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="5" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" outline="1" outlineData="1" compactData="0" multipleFieldFilters="0" chartFormat="5">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9BE36CEB-A123-4E3F-9601-73D921FA7399}" name="PivotTable5" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="5" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" outline="1" outlineData="1" compactData="0" multipleFieldFilters="0" chartFormat="5">
   <location ref="A1:B6" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="12">
     <pivotField compact="0" showAll="0"/>
@@ -18414,7 +18414,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C7B9CF9F-631C-4B69-91CF-83CE3ED91175}" name="PivotTable9" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="5" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C7B9CF9F-631C-4B69-91CF-83CE3ED91175}" name="PivotTable9" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="5" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7">
   <location ref="A45:B56" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="12">
     <pivotField showAll="0"/>
@@ -19152,7 +19152,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C31763EB-696F-480D-B4DC-EAE69ACA3975}" name="PivotTable7" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="5" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" outline="1" outlineData="1" compactData="0" multipleFieldFilters="0" chartFormat="19">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C31763EB-696F-480D-B4DC-EAE69ACA3975}" name="PivotTable7" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="5" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" outline="1" outlineData="1" compactData="0" multipleFieldFilters="0" chartFormat="19">
   <location ref="A30:B37" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="12">
     <pivotField compact="0" showAll="0"/>
@@ -19692,7 +19692,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0BD1A1B0-673B-4B02-80C5-F8466525BD1E}" name="PivotTable6" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="5" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" outline="1" outlineData="1" compactData="0" multipleFieldFilters="0" chartFormat="18">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0BD1A1B0-673B-4B02-80C5-F8466525BD1E}" name="PivotTable6" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="5" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" outline="1" outlineData="1" compactData="0" multipleFieldFilters="0" chartFormat="18">
   <location ref="A15:B26" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="12">
     <pivotField compact="0" showAll="0"/>
@@ -20515,7 +20515,7 @@
       </c>
       <c r="K2" s="33">
         <f ca="1">IF(ROW()&lt;=151,DATE(2024,RANDBETWEEN(1,12),RANDBETWEEN(1,28)),DATE(2025,RANDBETWEEN(1,12),RANDBETWEEN(1,28)))</f>
-        <v>45549</v>
+        <v>45580</v>
       </c>
       <c r="L2" s="45" t="str">
         <f>CHOOSE(MOD(ROW()-2,4)+1,"North","South","East","West")</f>
@@ -20557,7 +20557,7 @@
       </c>
       <c r="K3" s="33">
         <f t="shared" ref="K3:K66" ca="1" si="2">IF(ROW()&lt;=151,DATE(2024,RANDBETWEEN(1,12),RANDBETWEEN(1,28)),DATE(2025,RANDBETWEEN(1,12),RANDBETWEEN(1,28)))</f>
-        <v>45394</v>
+        <v>45568</v>
       </c>
       <c r="L3" s="45" t="str">
         <f t="shared" ref="L3:L66" si="3">CHOOSE(MOD(ROW()-2,4)+1,"North","South","East","West")</f>
@@ -20599,7 +20599,7 @@
       </c>
       <c r="K4" s="33">
         <f t="shared" ca="1" si="2"/>
-        <v>45330</v>
+        <v>45314</v>
       </c>
       <c r="L4" s="45" t="str">
         <f t="shared" si="3"/>
@@ -20641,7 +20641,7 @@
       </c>
       <c r="K5" s="33">
         <f t="shared" ca="1" si="2"/>
-        <v>45617</v>
+        <v>45632</v>
       </c>
       <c r="L5" s="45" t="str">
         <f t="shared" si="3"/>
@@ -20683,7 +20683,7 @@
       </c>
       <c r="K6" s="33">
         <f t="shared" ca="1" si="2"/>
-        <v>45366</v>
+        <v>45578</v>
       </c>
       <c r="L6" s="45" t="str">
         <f t="shared" si="3"/>
@@ -20725,7 +20725,7 @@
       </c>
       <c r="K7" s="33">
         <f t="shared" ca="1" si="2"/>
-        <v>45407</v>
+        <v>45332</v>
       </c>
       <c r="L7" s="45" t="str">
         <f t="shared" si="3"/>
@@ -20767,7 +20767,7 @@
       </c>
       <c r="K8" s="33">
         <f t="shared" ca="1" si="2"/>
-        <v>45529</v>
+        <v>45613</v>
       </c>
       <c r="L8" s="45" t="str">
         <f t="shared" si="3"/>
@@ -20809,7 +20809,7 @@
       </c>
       <c r="K9" s="33">
         <f t="shared" ca="1" si="2"/>
-        <v>45314</v>
+        <v>45598</v>
       </c>
       <c r="L9" s="45" t="str">
         <f t="shared" si="3"/>
@@ -20851,7 +20851,7 @@
       </c>
       <c r="K10" s="33">
         <f t="shared" ca="1" si="2"/>
-        <v>45357</v>
+        <v>45501</v>
       </c>
       <c r="L10" s="45" t="str">
         <f t="shared" si="3"/>
@@ -20893,7 +20893,7 @@
       </c>
       <c r="K11" s="33">
         <f t="shared" ca="1" si="2"/>
-        <v>45408</v>
+        <v>45540</v>
       </c>
       <c r="L11" s="45" t="str">
         <f t="shared" si="3"/>
@@ -20935,7 +20935,7 @@
       </c>
       <c r="K12" s="33">
         <f t="shared" ca="1" si="2"/>
-        <v>45377</v>
+        <v>45622</v>
       </c>
       <c r="L12" s="45" t="str">
         <f t="shared" si="3"/>
@@ -20977,7 +20977,7 @@
       </c>
       <c r="K13" s="33">
         <f t="shared" ca="1" si="2"/>
-        <v>45417</v>
+        <v>45433</v>
       </c>
       <c r="L13" s="45" t="str">
         <f t="shared" si="3"/>
@@ -21019,7 +21019,7 @@
       </c>
       <c r="K14" s="33">
         <f t="shared" ca="1" si="2"/>
-        <v>45606</v>
+        <v>45454</v>
       </c>
       <c r="L14" s="45" t="str">
         <f t="shared" si="3"/>
@@ -21061,7 +21061,7 @@
       </c>
       <c r="K15" s="33">
         <f t="shared" ca="1" si="2"/>
-        <v>45413</v>
+        <v>45621</v>
       </c>
       <c r="L15" s="45" t="str">
         <f t="shared" si="3"/>
@@ -21103,7 +21103,7 @@
       </c>
       <c r="K16" s="33">
         <f t="shared" ca="1" si="2"/>
-        <v>45481</v>
+        <v>45425</v>
       </c>
       <c r="L16" s="45" t="str">
         <f t="shared" si="3"/>
@@ -21145,7 +21145,7 @@
       </c>
       <c r="K17" s="33">
         <f t="shared" ca="1" si="2"/>
-        <v>45548</v>
+        <v>45645</v>
       </c>
       <c r="L17" s="45" t="str">
         <f t="shared" si="3"/>
@@ -21187,7 +21187,7 @@
       </c>
       <c r="K18" s="33">
         <f t="shared" ca="1" si="2"/>
-        <v>45493</v>
+        <v>45524</v>
       </c>
       <c r="L18" s="45" t="str">
         <f t="shared" si="3"/>
@@ -21229,7 +21229,7 @@
       </c>
       <c r="K19" s="33">
         <f t="shared" ca="1" si="2"/>
-        <v>45324</v>
+        <v>45332</v>
       </c>
       <c r="L19" s="45" t="str">
         <f t="shared" si="3"/>
@@ -21271,7 +21271,7 @@
       </c>
       <c r="K20" s="33">
         <f t="shared" ca="1" si="2"/>
-        <v>45341</v>
+        <v>45567</v>
       </c>
       <c r="L20" s="45" t="str">
         <f t="shared" si="3"/>
@@ -21313,7 +21313,7 @@
       </c>
       <c r="K21" s="33">
         <f t="shared" ca="1" si="2"/>
-        <v>45358</v>
+        <v>45415</v>
       </c>
       <c r="L21" s="45" t="str">
         <f t="shared" si="3"/>
@@ -21355,7 +21355,7 @@
       </c>
       <c r="K22" s="33">
         <f t="shared" ca="1" si="2"/>
-        <v>45622</v>
+        <v>45567</v>
       </c>
       <c r="L22" s="45" t="str">
         <f t="shared" si="3"/>
@@ -21397,7 +21397,7 @@
       </c>
       <c r="K23" s="33">
         <f t="shared" ca="1" si="2"/>
-        <v>45603</v>
+        <v>45592</v>
       </c>
       <c r="L23" s="45" t="str">
         <f t="shared" si="3"/>
@@ -21439,7 +21439,7 @@
       </c>
       <c r="K24" s="33">
         <f t="shared" ca="1" si="2"/>
-        <v>45298</v>
+        <v>45566</v>
       </c>
       <c r="L24" s="45" t="str">
         <f t="shared" si="3"/>
@@ -21481,7 +21481,7 @@
       </c>
       <c r="K25" s="33">
         <f t="shared" ca="1" si="2"/>
-        <v>45334</v>
+        <v>45464</v>
       </c>
       <c r="L25" s="45" t="str">
         <f t="shared" si="3"/>
@@ -21523,7 +21523,7 @@
       </c>
       <c r="K26" s="33">
         <f t="shared" ca="1" si="2"/>
-        <v>45518</v>
+        <v>45345</v>
       </c>
       <c r="L26" s="45" t="str">
         <f t="shared" si="3"/>
@@ -21565,7 +21565,7 @@
       </c>
       <c r="K27" s="33">
         <f t="shared" ca="1" si="2"/>
-        <v>45328</v>
+        <v>45311</v>
       </c>
       <c r="L27" s="45" t="str">
         <f t="shared" si="3"/>
@@ -21607,7 +21607,7 @@
       </c>
       <c r="K28" s="33">
         <f t="shared" ca="1" si="2"/>
-        <v>45589</v>
+        <v>45348</v>
       </c>
       <c r="L28" s="45" t="str">
         <f t="shared" si="3"/>
@@ -21649,7 +21649,7 @@
       </c>
       <c r="K29" s="33">
         <f t="shared" ca="1" si="2"/>
-        <v>45646</v>
+        <v>45559</v>
       </c>
       <c r="L29" s="45" t="str">
         <f t="shared" si="3"/>
@@ -21691,7 +21691,7 @@
       </c>
       <c r="K30" s="33">
         <f t="shared" ca="1" si="2"/>
-        <v>45438</v>
+        <v>45517</v>
       </c>
       <c r="L30" s="45" t="str">
         <f t="shared" si="3"/>
@@ -21733,7 +21733,7 @@
       </c>
       <c r="K31" s="33">
         <f t="shared" ca="1" si="2"/>
-        <v>45449</v>
+        <v>45294</v>
       </c>
       <c r="L31" s="45" t="str">
         <f t="shared" si="3"/>
@@ -21775,7 +21775,7 @@
       </c>
       <c r="K32" s="33">
         <f t="shared" ca="1" si="2"/>
-        <v>45463</v>
+        <v>45357</v>
       </c>
       <c r="L32" s="45" t="str">
         <f t="shared" si="3"/>
@@ -21817,7 +21817,7 @@
       </c>
       <c r="K33" s="33">
         <f t="shared" ca="1" si="2"/>
-        <v>45637</v>
+        <v>45605</v>
       </c>
       <c r="L33" s="45" t="str">
         <f t="shared" si="3"/>
@@ -21859,7 +21859,7 @@
       </c>
       <c r="K34" s="33">
         <f t="shared" ca="1" si="2"/>
-        <v>45483</v>
+        <v>45477</v>
       </c>
       <c r="L34" s="45" t="str">
         <f t="shared" si="3"/>
@@ -21901,7 +21901,7 @@
       </c>
       <c r="K35" s="33">
         <f t="shared" ca="1" si="2"/>
-        <v>45358</v>
+        <v>45632</v>
       </c>
       <c r="L35" s="45" t="str">
         <f t="shared" si="3"/>
@@ -21943,7 +21943,7 @@
       </c>
       <c r="K36" s="33">
         <f t="shared" ca="1" si="2"/>
-        <v>45496</v>
+        <v>45415</v>
       </c>
       <c r="L36" s="45" t="str">
         <f t="shared" si="3"/>
@@ -21985,7 +21985,7 @@
       </c>
       <c r="K37" s="33">
         <f t="shared" ca="1" si="2"/>
-        <v>45584</v>
+        <v>45426</v>
       </c>
       <c r="L37" s="45" t="str">
         <f t="shared" si="3"/>
@@ -22027,7 +22027,7 @@
       </c>
       <c r="K38" s="33">
         <f t="shared" ca="1" si="2"/>
-        <v>45318</v>
+        <v>45460</v>
       </c>
       <c r="L38" s="45" t="str">
         <f t="shared" si="3"/>
@@ -22069,7 +22069,7 @@
       </c>
       <c r="K39" s="33">
         <f t="shared" ca="1" si="2"/>
-        <v>45454</v>
+        <v>45437</v>
       </c>
       <c r="L39" s="45" t="str">
         <f t="shared" si="3"/>
@@ -22111,7 +22111,7 @@
       </c>
       <c r="K40" s="33">
         <f t="shared" ca="1" si="2"/>
-        <v>45379</v>
+        <v>45598</v>
       </c>
       <c r="L40" s="45" t="str">
         <f t="shared" si="3"/>
@@ -22153,7 +22153,7 @@
       </c>
       <c r="K41" s="33">
         <f t="shared" ca="1" si="2"/>
-        <v>45549</v>
+        <v>45536</v>
       </c>
       <c r="L41" s="45" t="str">
         <f t="shared" si="3"/>
@@ -22195,7 +22195,7 @@
       </c>
       <c r="K42" s="33">
         <f t="shared" ca="1" si="2"/>
-        <v>45476</v>
+        <v>45384</v>
       </c>
       <c r="L42" s="45" t="str">
         <f t="shared" si="3"/>
@@ -22237,7 +22237,7 @@
       </c>
       <c r="K43" s="33">
         <f t="shared" ca="1" si="2"/>
-        <v>45513</v>
+        <v>45570</v>
       </c>
       <c r="L43" s="45" t="str">
         <f t="shared" si="3"/>
@@ -22279,7 +22279,7 @@
       </c>
       <c r="K44" s="33">
         <f t="shared" ca="1" si="2"/>
-        <v>45525</v>
+        <v>45464</v>
       </c>
       <c r="L44" s="45" t="str">
         <f t="shared" si="3"/>
@@ -22321,7 +22321,7 @@
       </c>
       <c r="K45" s="33">
         <f t="shared" ca="1" si="2"/>
-        <v>45434</v>
+        <v>45422</v>
       </c>
       <c r="L45" s="45" t="str">
         <f t="shared" si="3"/>
@@ -22363,7 +22363,7 @@
       </c>
       <c r="K46" s="33">
         <f t="shared" ca="1" si="2"/>
-        <v>45438</v>
+        <v>45572</v>
       </c>
       <c r="L46" s="45" t="str">
         <f t="shared" si="3"/>
@@ -22405,7 +22405,7 @@
       </c>
       <c r="K47" s="33">
         <f t="shared" ca="1" si="2"/>
-        <v>45369</v>
+        <v>45619</v>
       </c>
       <c r="L47" s="45" t="str">
         <f t="shared" si="3"/>
@@ -22447,7 +22447,7 @@
       </c>
       <c r="K48" s="33">
         <f t="shared" ca="1" si="2"/>
-        <v>45584</v>
+        <v>45538</v>
       </c>
       <c r="L48" s="45" t="str">
         <f t="shared" si="3"/>
@@ -22489,7 +22489,7 @@
       </c>
       <c r="K49" s="33">
         <f t="shared" ca="1" si="2"/>
-        <v>45432</v>
+        <v>45413</v>
       </c>
       <c r="L49" s="45" t="str">
         <f t="shared" si="3"/>
@@ -22531,7 +22531,7 @@
       </c>
       <c r="K50" s="33">
         <f t="shared" ca="1" si="2"/>
-        <v>45642</v>
+        <v>45598</v>
       </c>
       <c r="L50" s="45" t="str">
         <f t="shared" si="3"/>
@@ -22573,7 +22573,7 @@
       </c>
       <c r="K51" s="33">
         <f t="shared" ca="1" si="2"/>
-        <v>45405</v>
+        <v>45305</v>
       </c>
       <c r="L51" s="45" t="str">
         <f t="shared" si="3"/>
@@ -22615,7 +22615,7 @@
       </c>
       <c r="K52" s="33">
         <f t="shared" ca="1" si="2"/>
-        <v>45331</v>
+        <v>45573</v>
       </c>
       <c r="L52" s="45" t="str">
         <f t="shared" si="3"/>
@@ -22657,7 +22657,7 @@
       </c>
       <c r="K53" s="33">
         <f t="shared" ca="1" si="2"/>
-        <v>45455</v>
+        <v>45464</v>
       </c>
       <c r="L53" s="45" t="str">
         <f t="shared" si="3"/>
@@ -22699,7 +22699,7 @@
       </c>
       <c r="K54" s="33">
         <f t="shared" ca="1" si="2"/>
-        <v>45624</v>
+        <v>45517</v>
       </c>
       <c r="L54" s="45" t="str">
         <f t="shared" si="3"/>
@@ -22741,7 +22741,7 @@
       </c>
       <c r="K55" s="33">
         <f t="shared" ca="1" si="2"/>
-        <v>45559</v>
+        <v>45450</v>
       </c>
       <c r="L55" s="45" t="str">
         <f t="shared" si="3"/>
@@ -22783,7 +22783,7 @@
       </c>
       <c r="K56" s="33">
         <f t="shared" ca="1" si="2"/>
-        <v>45637</v>
+        <v>45409</v>
       </c>
       <c r="L56" s="45" t="str">
         <f t="shared" si="3"/>
@@ -22825,7 +22825,7 @@
       </c>
       <c r="K57" s="33">
         <f t="shared" ca="1" si="2"/>
-        <v>45294</v>
+        <v>45582</v>
       </c>
       <c r="L57" s="45" t="str">
         <f t="shared" si="3"/>
@@ -22867,7 +22867,7 @@
       </c>
       <c r="K58" s="33">
         <f t="shared" ca="1" si="2"/>
-        <v>45541</v>
+        <v>45571</v>
       </c>
       <c r="L58" s="45" t="str">
         <f t="shared" si="3"/>
@@ -22909,7 +22909,7 @@
       </c>
       <c r="K59" s="33">
         <f t="shared" ca="1" si="2"/>
-        <v>45422</v>
+        <v>45391</v>
       </c>
       <c r="L59" s="45" t="str">
         <f t="shared" si="3"/>
@@ -22951,7 +22951,7 @@
       </c>
       <c r="K60" s="33">
         <f t="shared" ca="1" si="2"/>
-        <v>45608</v>
+        <v>45437</v>
       </c>
       <c r="L60" s="45" t="str">
         <f t="shared" si="3"/>
@@ -22993,7 +22993,7 @@
       </c>
       <c r="K61" s="33">
         <f t="shared" ca="1" si="2"/>
-        <v>45450</v>
+        <v>45539</v>
       </c>
       <c r="L61" s="45" t="str">
         <f t="shared" si="3"/>
@@ -23035,7 +23035,7 @@
       </c>
       <c r="K62" s="33">
         <f t="shared" ca="1" si="2"/>
-        <v>45308</v>
+        <v>45316</v>
       </c>
       <c r="L62" s="45" t="str">
         <f t="shared" si="3"/>
@@ -23077,7 +23077,7 @@
       </c>
       <c r="K63" s="33">
         <f t="shared" ca="1" si="2"/>
-        <v>45336</v>
+        <v>45492</v>
       </c>
       <c r="L63" s="45" t="str">
         <f t="shared" si="3"/>
@@ -23119,7 +23119,7 @@
       </c>
       <c r="K64" s="33">
         <f t="shared" ca="1" si="2"/>
-        <v>45495</v>
+        <v>45579</v>
       </c>
       <c r="L64" s="45" t="str">
         <f t="shared" si="3"/>
@@ -23161,7 +23161,7 @@
       </c>
       <c r="K65" s="33">
         <f t="shared" ca="1" si="2"/>
-        <v>45366</v>
+        <v>45485</v>
       </c>
       <c r="L65" s="45" t="str">
         <f t="shared" si="3"/>
@@ -23203,7 +23203,7 @@
       </c>
       <c r="K66" s="33">
         <f t="shared" ca="1" si="2"/>
-        <v>45318</v>
+        <v>45622</v>
       </c>
       <c r="L66" s="45" t="str">
         <f t="shared" si="3"/>
@@ -23245,7 +23245,7 @@
       </c>
       <c r="K67" s="33">
         <f t="shared" ref="K67:K130" ca="1" si="6">IF(ROW()&lt;=151,DATE(2024,RANDBETWEEN(1,12),RANDBETWEEN(1,28)),DATE(2025,RANDBETWEEN(1,12),RANDBETWEEN(1,28)))</f>
-        <v>45646</v>
+        <v>45344</v>
       </c>
       <c r="L67" s="45" t="str">
         <f t="shared" ref="L67:L130" si="7">CHOOSE(MOD(ROW()-2,4)+1,"North","South","East","West")</f>
@@ -23287,7 +23287,7 @@
       </c>
       <c r="K68" s="33">
         <f t="shared" ca="1" si="6"/>
-        <v>45342</v>
+        <v>45650</v>
       </c>
       <c r="L68" s="45" t="str">
         <f t="shared" si="7"/>
@@ -23329,7 +23329,7 @@
       </c>
       <c r="K69" s="33">
         <f t="shared" ca="1" si="6"/>
-        <v>45563</v>
+        <v>45649</v>
       </c>
       <c r="L69" s="45" t="str">
         <f t="shared" si="7"/>
@@ -23371,7 +23371,7 @@
       </c>
       <c r="K70" s="33">
         <f t="shared" ca="1" si="6"/>
-        <v>45540</v>
+        <v>45479</v>
       </c>
       <c r="L70" s="45" t="str">
         <f t="shared" si="7"/>
@@ -23413,7 +23413,7 @@
       </c>
       <c r="K71" s="33">
         <f t="shared" ca="1" si="6"/>
-        <v>45549</v>
+        <v>45588</v>
       </c>
       <c r="L71" s="45" t="str">
         <f t="shared" si="7"/>
@@ -23455,7 +23455,7 @@
       </c>
       <c r="K72" s="33">
         <f t="shared" ca="1" si="6"/>
-        <v>45479</v>
+        <v>45466</v>
       </c>
       <c r="L72" s="45" t="str">
         <f t="shared" si="7"/>
@@ -23497,7 +23497,7 @@
       </c>
       <c r="K73" s="33">
         <f t="shared" ca="1" si="6"/>
-        <v>45597</v>
+        <v>45620</v>
       </c>
       <c r="L73" s="45" t="str">
         <f t="shared" si="7"/>
@@ -23539,7 +23539,7 @@
       </c>
       <c r="K74" s="33">
         <f t="shared" ca="1" si="6"/>
-        <v>45556</v>
+        <v>45383</v>
       </c>
       <c r="L74" s="45" t="str">
         <f t="shared" si="7"/>
@@ -23581,7 +23581,7 @@
       </c>
       <c r="K75" s="33">
         <f t="shared" ca="1" si="6"/>
-        <v>45583</v>
+        <v>45617</v>
       </c>
       <c r="L75" s="45" t="str">
         <f t="shared" si="7"/>
@@ -23623,7 +23623,7 @@
       </c>
       <c r="K76" s="33">
         <f t="shared" ca="1" si="6"/>
-        <v>45371</v>
+        <v>45600</v>
       </c>
       <c r="L76" s="45" t="str">
         <f t="shared" si="7"/>
@@ -23665,7 +23665,7 @@
       </c>
       <c r="K77" s="33">
         <f t="shared" ca="1" si="6"/>
-        <v>45338</v>
+        <v>45584</v>
       </c>
       <c r="L77" s="45" t="str">
         <f t="shared" si="7"/>
@@ -23707,7 +23707,7 @@
       </c>
       <c r="K78" s="33">
         <f t="shared" ca="1" si="6"/>
-        <v>45579</v>
+        <v>45646</v>
       </c>
       <c r="L78" s="45" t="str">
         <f t="shared" si="7"/>
@@ -23749,7 +23749,7 @@
       </c>
       <c r="K79" s="33">
         <f t="shared" ca="1" si="6"/>
-        <v>45375</v>
+        <v>45629</v>
       </c>
       <c r="L79" s="45" t="str">
         <f t="shared" si="7"/>
@@ -23791,7 +23791,7 @@
       </c>
       <c r="K80" s="33">
         <f t="shared" ca="1" si="6"/>
-        <v>45514</v>
+        <v>45480</v>
       </c>
       <c r="L80" s="45" t="str">
         <f t="shared" si="7"/>
@@ -23833,7 +23833,7 @@
       </c>
       <c r="K81" s="33">
         <f t="shared" ca="1" si="6"/>
-        <v>45409</v>
+        <v>45492</v>
       </c>
       <c r="L81" s="45" t="str">
         <f t="shared" si="7"/>
@@ -23875,7 +23875,7 @@
       </c>
       <c r="K82" s="33">
         <f t="shared" ca="1" si="6"/>
-        <v>45346</v>
+        <v>45500</v>
       </c>
       <c r="L82" s="45" t="str">
         <f t="shared" si="7"/>
@@ -23917,7 +23917,7 @@
       </c>
       <c r="K83" s="33">
         <f t="shared" ca="1" si="6"/>
-        <v>45532</v>
+        <v>45491</v>
       </c>
       <c r="L83" s="45" t="str">
         <f t="shared" si="7"/>
@@ -23959,7 +23959,7 @@
       </c>
       <c r="K84" s="33">
         <f t="shared" ca="1" si="6"/>
-        <v>45487</v>
+        <v>45347</v>
       </c>
       <c r="L84" s="45" t="str">
         <f t="shared" si="7"/>
@@ -24001,7 +24001,7 @@
       </c>
       <c r="K85" s="33">
         <f t="shared" ca="1" si="6"/>
-        <v>45369</v>
+        <v>45488</v>
       </c>
       <c r="L85" s="45" t="str">
         <f t="shared" si="7"/>
@@ -24043,7 +24043,7 @@
       </c>
       <c r="K86" s="33">
         <f t="shared" ca="1" si="6"/>
-        <v>45326</v>
+        <v>45337</v>
       </c>
       <c r="L86" s="45" t="str">
         <f t="shared" si="7"/>
@@ -24085,7 +24085,7 @@
       </c>
       <c r="K87" s="33">
         <f t="shared" ca="1" si="6"/>
-        <v>45485</v>
+        <v>45409</v>
       </c>
       <c r="L87" s="45" t="str">
         <f t="shared" si="7"/>
@@ -24127,7 +24127,7 @@
       </c>
       <c r="K88" s="33">
         <f t="shared" ca="1" si="6"/>
-        <v>45413</v>
+        <v>45627</v>
       </c>
       <c r="L88" s="45" t="str">
         <f t="shared" si="7"/>
@@ -24169,7 +24169,7 @@
       </c>
       <c r="K89" s="33">
         <f t="shared" ca="1" si="6"/>
-        <v>45591</v>
+        <v>45374</v>
       </c>
       <c r="L89" s="45" t="str">
         <f t="shared" si="7"/>
@@ -24211,7 +24211,7 @@
       </c>
       <c r="K90" s="33">
         <f t="shared" ca="1" si="6"/>
-        <v>45492</v>
+        <v>45372</v>
       </c>
       <c r="L90" s="45" t="str">
         <f t="shared" si="7"/>
@@ -24253,7 +24253,7 @@
       </c>
       <c r="K91" s="33">
         <f t="shared" ca="1" si="6"/>
-        <v>45653</v>
+        <v>45340</v>
       </c>
       <c r="L91" s="45" t="str">
         <f t="shared" si="7"/>
@@ -24295,7 +24295,7 @@
       </c>
       <c r="K92" s="33">
         <f t="shared" ca="1" si="6"/>
-        <v>45295</v>
+        <v>45408</v>
       </c>
       <c r="L92" s="45" t="str">
         <f t="shared" si="7"/>
@@ -24337,7 +24337,7 @@
       </c>
       <c r="K93" s="33">
         <f t="shared" ca="1" si="6"/>
-        <v>45391</v>
+        <v>45577</v>
       </c>
       <c r="L93" s="45" t="str">
         <f t="shared" si="7"/>
@@ -24379,7 +24379,7 @@
       </c>
       <c r="K94" s="33">
         <f t="shared" ca="1" si="6"/>
-        <v>45335</v>
+        <v>45315</v>
       </c>
       <c r="L94" s="45" t="str">
         <f t="shared" si="7"/>
@@ -24421,7 +24421,7 @@
       </c>
       <c r="K95" s="33">
         <f t="shared" ca="1" si="6"/>
-        <v>45569</v>
+        <v>45553</v>
       </c>
       <c r="L95" s="45" t="str">
         <f t="shared" si="7"/>
@@ -24463,7 +24463,7 @@
       </c>
       <c r="K96" s="33">
         <f t="shared" ca="1" si="6"/>
-        <v>45317</v>
+        <v>45363</v>
       </c>
       <c r="L96" s="45" t="str">
         <f t="shared" si="7"/>
@@ -24505,7 +24505,7 @@
       </c>
       <c r="K97" s="33">
         <f t="shared" ca="1" si="6"/>
-        <v>45431</v>
+        <v>45294</v>
       </c>
       <c r="L97" s="45" t="str">
         <f t="shared" si="7"/>
@@ -24547,7 +24547,7 @@
       </c>
       <c r="K98" s="33">
         <f t="shared" ca="1" si="6"/>
-        <v>45519</v>
+        <v>45404</v>
       </c>
       <c r="L98" s="45" t="str">
         <f t="shared" si="7"/>
@@ -24589,7 +24589,7 @@
       </c>
       <c r="K99" s="33">
         <f t="shared" ca="1" si="6"/>
-        <v>45507</v>
+        <v>45307</v>
       </c>
       <c r="L99" s="45" t="str">
         <f t="shared" si="7"/>
@@ -24631,7 +24631,7 @@
       </c>
       <c r="K100" s="33">
         <f t="shared" ca="1" si="6"/>
-        <v>45393</v>
+        <v>45456</v>
       </c>
       <c r="L100" s="45" t="str">
         <f t="shared" si="7"/>
@@ -24673,7 +24673,7 @@
       </c>
       <c r="K101" s="33">
         <f t="shared" ca="1" si="6"/>
-        <v>45451</v>
+        <v>45593</v>
       </c>
       <c r="L101" s="45" t="str">
         <f t="shared" si="7"/>
@@ -24715,7 +24715,7 @@
       </c>
       <c r="K102" s="33">
         <f t="shared" ca="1" si="6"/>
-        <v>45408</v>
+        <v>45629</v>
       </c>
       <c r="L102" s="45" t="str">
         <f t="shared" si="7"/>
@@ -24757,7 +24757,7 @@
       </c>
       <c r="K103" s="33">
         <f t="shared" ca="1" si="6"/>
-        <v>45385</v>
+        <v>45524</v>
       </c>
       <c r="L103" s="45" t="str">
         <f t="shared" si="7"/>
@@ -24799,7 +24799,7 @@
       </c>
       <c r="K104" s="33">
         <f t="shared" ca="1" si="6"/>
-        <v>45537</v>
+        <v>45295</v>
       </c>
       <c r="L104" s="45" t="str">
         <f t="shared" si="7"/>
@@ -24841,7 +24841,7 @@
       </c>
       <c r="K105" s="33">
         <f t="shared" ca="1" si="6"/>
-        <v>45652</v>
+        <v>45629</v>
       </c>
       <c r="L105" s="45" t="str">
         <f t="shared" si="7"/>
@@ -24883,7 +24883,7 @@
       </c>
       <c r="K106" s="33">
         <f t="shared" ca="1" si="6"/>
-        <v>45416</v>
+        <v>45488</v>
       </c>
       <c r="L106" s="45" t="str">
         <f t="shared" si="7"/>
@@ -24925,7 +24925,7 @@
       </c>
       <c r="K107" s="33">
         <f t="shared" ca="1" si="6"/>
-        <v>45313</v>
+        <v>45352</v>
       </c>
       <c r="L107" s="45" t="str">
         <f t="shared" si="7"/>
@@ -24967,7 +24967,7 @@
       </c>
       <c r="K108" s="33">
         <f t="shared" ca="1" si="6"/>
-        <v>45493</v>
+        <v>45588</v>
       </c>
       <c r="L108" s="45" t="str">
         <f t="shared" si="7"/>
@@ -25009,7 +25009,7 @@
       </c>
       <c r="K109" s="33">
         <f t="shared" ca="1" si="6"/>
-        <v>45390</v>
+        <v>45336</v>
       </c>
       <c r="L109" s="45" t="str">
         <f t="shared" si="7"/>
@@ -25051,7 +25051,7 @@
       </c>
       <c r="K110" s="33">
         <f t="shared" ca="1" si="6"/>
-        <v>45623</v>
+        <v>45631</v>
       </c>
       <c r="L110" s="45" t="str">
         <f t="shared" si="7"/>
@@ -25093,7 +25093,7 @@
       </c>
       <c r="K111" s="33">
         <f t="shared" ca="1" si="6"/>
-        <v>45550</v>
+        <v>45344</v>
       </c>
       <c r="L111" s="45" t="str">
         <f t="shared" si="7"/>
@@ -25135,7 +25135,7 @@
       </c>
       <c r="K112" s="33">
         <f t="shared" ca="1" si="6"/>
-        <v>45580</v>
+        <v>45483</v>
       </c>
       <c r="L112" s="45" t="str">
         <f t="shared" si="7"/>
@@ -25177,7 +25177,7 @@
       </c>
       <c r="K113" s="33">
         <f t="shared" ca="1" si="6"/>
-        <v>45514</v>
+        <v>45634</v>
       </c>
       <c r="L113" s="45" t="str">
         <f t="shared" si="7"/>
@@ -25219,7 +25219,7 @@
       </c>
       <c r="K114" s="33">
         <f t="shared" ca="1" si="6"/>
-        <v>45578</v>
+        <v>45581</v>
       </c>
       <c r="L114" s="45" t="str">
         <f t="shared" si="7"/>
@@ -25261,7 +25261,7 @@
       </c>
       <c r="K115" s="33">
         <f t="shared" ca="1" si="6"/>
-        <v>45624</v>
+        <v>45332</v>
       </c>
       <c r="L115" s="45" t="str">
         <f t="shared" si="7"/>
@@ -25303,7 +25303,7 @@
       </c>
       <c r="K116" s="33">
         <f t="shared" ca="1" si="6"/>
-        <v>45383</v>
+        <v>45377</v>
       </c>
       <c r="L116" s="45" t="str">
         <f t="shared" si="7"/>
@@ -25345,7 +25345,7 @@
       </c>
       <c r="K117" s="33">
         <f t="shared" ca="1" si="6"/>
-        <v>45485</v>
+        <v>45526</v>
       </c>
       <c r="L117" s="45" t="str">
         <f t="shared" si="7"/>
@@ -25387,7 +25387,7 @@
       </c>
       <c r="K118" s="33">
         <f t="shared" ca="1" si="6"/>
-        <v>45593</v>
+        <v>45338</v>
       </c>
       <c r="L118" s="45" t="str">
         <f t="shared" si="7"/>
@@ -25429,7 +25429,7 @@
       </c>
       <c r="K119" s="33">
         <f t="shared" ca="1" si="6"/>
-        <v>45539</v>
+        <v>45352</v>
       </c>
       <c r="L119" s="45" t="str">
         <f t="shared" si="7"/>
@@ -25471,7 +25471,7 @@
       </c>
       <c r="K120" s="33">
         <f t="shared" ca="1" si="6"/>
-        <v>45345</v>
+        <v>45317</v>
       </c>
       <c r="L120" s="45" t="str">
         <f t="shared" si="7"/>
@@ -25513,7 +25513,7 @@
       </c>
       <c r="K121" s="33">
         <f t="shared" ca="1" si="6"/>
-        <v>45294</v>
+        <v>45418</v>
       </c>
       <c r="L121" s="45" t="str">
         <f t="shared" si="7"/>
@@ -25555,7 +25555,7 @@
       </c>
       <c r="K122" s="33">
         <f t="shared" ca="1" si="6"/>
-        <v>45480</v>
+        <v>45490</v>
       </c>
       <c r="L122" s="45" t="str">
         <f t="shared" si="7"/>
@@ -25597,7 +25597,7 @@
       </c>
       <c r="K123" s="33">
         <f t="shared" ca="1" si="6"/>
-        <v>45466</v>
+        <v>45447</v>
       </c>
       <c r="L123" s="45" t="str">
         <f t="shared" si="7"/>
@@ -25639,7 +25639,7 @@
       </c>
       <c r="K124" s="33">
         <f t="shared" ca="1" si="6"/>
-        <v>45527</v>
+        <v>45308</v>
       </c>
       <c r="L124" s="45" t="str">
         <f t="shared" si="7"/>
@@ -25681,7 +25681,7 @@
       </c>
       <c r="K125" s="33">
         <f t="shared" ca="1" si="6"/>
-        <v>45366</v>
+        <v>45360</v>
       </c>
       <c r="L125" s="45" t="str">
         <f t="shared" si="7"/>
@@ -25723,7 +25723,7 @@
       </c>
       <c r="K126" s="33">
         <f t="shared" ca="1" si="6"/>
-        <v>45494</v>
+        <v>45645</v>
       </c>
       <c r="L126" s="45" t="str">
         <f t="shared" si="7"/>
@@ -25765,7 +25765,7 @@
       </c>
       <c r="K127" s="33">
         <f t="shared" ca="1" si="6"/>
-        <v>45640</v>
+        <v>45421</v>
       </c>
       <c r="L127" s="45" t="str">
         <f t="shared" si="7"/>
@@ -25807,7 +25807,7 @@
       </c>
       <c r="K128" s="33">
         <f t="shared" ca="1" si="6"/>
-        <v>45641</v>
+        <v>45330</v>
       </c>
       <c r="L128" s="45" t="str">
         <f t="shared" si="7"/>
@@ -25849,7 +25849,7 @@
       </c>
       <c r="K129" s="33">
         <f t="shared" ca="1" si="6"/>
-        <v>45486</v>
+        <v>45581</v>
       </c>
       <c r="L129" s="45" t="str">
         <f t="shared" si="7"/>
@@ -25891,7 +25891,7 @@
       </c>
       <c r="K130" s="33">
         <f t="shared" ca="1" si="6"/>
-        <v>45317</v>
+        <v>45466</v>
       </c>
       <c r="L130" s="45" t="str">
         <f t="shared" si="7"/>
@@ -25933,7 +25933,7 @@
       </c>
       <c r="K131" s="33">
         <f t="shared" ref="K131:K194" ca="1" si="10">IF(ROW()&lt;=151,DATE(2024,RANDBETWEEN(1,12),RANDBETWEEN(1,28)),DATE(2025,RANDBETWEEN(1,12),RANDBETWEEN(1,28)))</f>
-        <v>45545</v>
+        <v>45458</v>
       </c>
       <c r="L131" s="45" t="str">
         <f t="shared" ref="L131:L194" si="11">CHOOSE(MOD(ROW()-2,4)+1,"North","South","East","West")</f>
@@ -25975,7 +25975,7 @@
       </c>
       <c r="K132" s="33">
         <f t="shared" ca="1" si="10"/>
-        <v>45374</v>
+        <v>45459</v>
       </c>
       <c r="L132" s="45" t="str">
         <f t="shared" si="11"/>
@@ -26017,7 +26017,7 @@
       </c>
       <c r="K133" s="33">
         <f t="shared" ca="1" si="10"/>
-        <v>45492</v>
+        <v>45297</v>
       </c>
       <c r="L133" s="45" t="str">
         <f t="shared" si="11"/>
@@ -26059,7 +26059,7 @@
       </c>
       <c r="K134" s="33">
         <f t="shared" ca="1" si="10"/>
-        <v>45444</v>
+        <v>45362</v>
       </c>
       <c r="L134" s="45" t="str">
         <f t="shared" si="11"/>
@@ -26101,7 +26101,7 @@
       </c>
       <c r="K135" s="33">
         <f t="shared" ca="1" si="10"/>
-        <v>45436</v>
+        <v>45581</v>
       </c>
       <c r="L135" s="45" t="str">
         <f t="shared" si="11"/>
@@ -26143,7 +26143,7 @@
       </c>
       <c r="K136" s="33">
         <f t="shared" ca="1" si="10"/>
-        <v>45455</v>
+        <v>45415</v>
       </c>
       <c r="L136" s="45" t="str">
         <f t="shared" si="11"/>
@@ -26185,7 +26185,7 @@
       </c>
       <c r="K137" s="33">
         <f t="shared" ca="1" si="10"/>
-        <v>45336</v>
+        <v>45475</v>
       </c>
       <c r="L137" s="45" t="str">
         <f t="shared" si="11"/>
@@ -26227,7 +26227,7 @@
       </c>
       <c r="K138" s="33">
         <f t="shared" ca="1" si="10"/>
-        <v>45641</v>
+        <v>45483</v>
       </c>
       <c r="L138" s="45" t="str">
         <f t="shared" si="11"/>
@@ -26269,7 +26269,7 @@
       </c>
       <c r="K139" s="33">
         <f t="shared" ca="1" si="10"/>
-        <v>45460</v>
+        <v>45642</v>
       </c>
       <c r="L139" s="45" t="str">
         <f t="shared" si="11"/>
@@ -26311,7 +26311,7 @@
       </c>
       <c r="K140" s="33">
         <f t="shared" ca="1" si="10"/>
-        <v>45587</v>
+        <v>45407</v>
       </c>
       <c r="L140" s="45" t="str">
         <f t="shared" si="11"/>
@@ -26353,7 +26353,7 @@
       </c>
       <c r="K141" s="33">
         <f t="shared" ca="1" si="10"/>
-        <v>45511</v>
+        <v>45451</v>
       </c>
       <c r="L141" s="45" t="str">
         <f t="shared" si="11"/>
@@ -26395,7 +26395,7 @@
       </c>
       <c r="K142" s="33">
         <f t="shared" ca="1" si="10"/>
-        <v>45621</v>
+        <v>45591</v>
       </c>
       <c r="L142" s="45" t="str">
         <f t="shared" si="11"/>
@@ -26437,7 +26437,7 @@
       </c>
       <c r="K143" s="33">
         <f t="shared" ca="1" si="10"/>
-        <v>45541</v>
+        <v>45375</v>
       </c>
       <c r="L143" s="45" t="str">
         <f t="shared" si="11"/>
@@ -26479,7 +26479,7 @@
       </c>
       <c r="K144" s="33">
         <f t="shared" ca="1" si="10"/>
-        <v>45396</v>
+        <v>45568</v>
       </c>
       <c r="L144" s="45" t="str">
         <f t="shared" si="11"/>
@@ -26521,7 +26521,7 @@
       </c>
       <c r="K145" s="33">
         <f t="shared" ca="1" si="10"/>
-        <v>45427</v>
+        <v>45458</v>
       </c>
       <c r="L145" s="45" t="str">
         <f t="shared" si="11"/>
@@ -26563,7 +26563,7 @@
       </c>
       <c r="K146" s="33">
         <f t="shared" ca="1" si="10"/>
-        <v>45410</v>
+        <v>45425</v>
       </c>
       <c r="L146" s="45" t="str">
         <f t="shared" si="11"/>
@@ -26605,7 +26605,7 @@
       </c>
       <c r="K147" s="33">
         <f t="shared" ca="1" si="10"/>
-        <v>45324</v>
+        <v>45359</v>
       </c>
       <c r="L147" s="45" t="str">
         <f t="shared" si="11"/>
@@ -26647,7 +26647,7 @@
       </c>
       <c r="K148" s="33">
         <f t="shared" ca="1" si="10"/>
-        <v>45507</v>
+        <v>45612</v>
       </c>
       <c r="L148" s="45" t="str">
         <f t="shared" si="11"/>
@@ -26689,7 +26689,7 @@
       </c>
       <c r="K149" s="33">
         <f t="shared" ca="1" si="10"/>
-        <v>45461</v>
+        <v>45463</v>
       </c>
       <c r="L149" s="45" t="str">
         <f t="shared" si="11"/>
@@ -26731,7 +26731,7 @@
       </c>
       <c r="K150" s="33">
         <f t="shared" ca="1" si="10"/>
-        <v>45309</v>
+        <v>45317</v>
       </c>
       <c r="L150" s="45" t="str">
         <f t="shared" si="11"/>
@@ -26773,7 +26773,7 @@
       </c>
       <c r="K151" s="33">
         <f t="shared" ca="1" si="10"/>
-        <v>45445</v>
+        <v>45644</v>
       </c>
       <c r="L151" s="45" t="str">
         <f t="shared" si="11"/>
@@ -26815,7 +26815,7 @@
       </c>
       <c r="K152" s="33">
         <f t="shared" ca="1" si="10"/>
-        <v>45816</v>
+        <v>45989</v>
       </c>
       <c r="L152" s="45" t="str">
         <f t="shared" si="11"/>
@@ -26857,7 +26857,7 @@
       </c>
       <c r="K153" s="33">
         <f t="shared" ca="1" si="10"/>
-        <v>45674</v>
+        <v>45704</v>
       </c>
       <c r="L153" s="45" t="str">
         <f t="shared" si="11"/>
@@ -26899,7 +26899,7 @@
       </c>
       <c r="K154" s="33">
         <f t="shared" ca="1" si="10"/>
-        <v>45905</v>
+        <v>45989</v>
       </c>
       <c r="L154" s="45" t="str">
         <f t="shared" si="11"/>
@@ -26941,7 +26941,7 @@
       </c>
       <c r="K155" s="33">
         <f t="shared" ca="1" si="10"/>
-        <v>45817</v>
+        <v>45989</v>
       </c>
       <c r="L155" s="45" t="str">
         <f t="shared" si="11"/>
@@ -26983,7 +26983,7 @@
       </c>
       <c r="K156" s="33">
         <f t="shared" ca="1" si="10"/>
-        <v>45934</v>
+        <v>45702</v>
       </c>
       <c r="L156" s="45" t="str">
         <f t="shared" si="11"/>
@@ -27025,7 +27025,7 @@
       </c>
       <c r="K157" s="33">
         <f t="shared" ca="1" si="10"/>
-        <v>45761</v>
+        <v>45964</v>
       </c>
       <c r="L157" s="45" t="str">
         <f t="shared" si="11"/>
@@ -27067,7 +27067,7 @@
       </c>
       <c r="K158" s="33">
         <f t="shared" ca="1" si="10"/>
-        <v>45981</v>
+        <v>45975</v>
       </c>
       <c r="L158" s="45" t="str">
         <f t="shared" si="11"/>
@@ -27109,7 +27109,7 @@
       </c>
       <c r="K159" s="33">
         <f t="shared" ca="1" si="10"/>
-        <v>45824</v>
+        <v>45872</v>
       </c>
       <c r="L159" s="45" t="str">
         <f t="shared" si="11"/>
@@ -27151,7 +27151,7 @@
       </c>
       <c r="K160" s="33">
         <f t="shared" ca="1" si="10"/>
-        <v>45986</v>
+        <v>45772</v>
       </c>
       <c r="L160" s="45" t="str">
         <f t="shared" si="11"/>
@@ -27193,7 +27193,7 @@
       </c>
       <c r="K161" s="33">
         <f t="shared" ca="1" si="10"/>
-        <v>45743</v>
+        <v>45873</v>
       </c>
       <c r="L161" s="45" t="str">
         <f t="shared" si="11"/>
@@ -27235,7 +27235,7 @@
       </c>
       <c r="K162" s="33">
         <f t="shared" ca="1" si="10"/>
-        <v>45785</v>
+        <v>45729</v>
       </c>
       <c r="L162" s="45" t="str">
         <f t="shared" si="11"/>
@@ -27277,7 +27277,7 @@
       </c>
       <c r="K163" s="33">
         <f t="shared" ca="1" si="10"/>
-        <v>46001</v>
+        <v>45755</v>
       </c>
       <c r="L163" s="45" t="str">
         <f t="shared" si="11"/>
@@ -27319,7 +27319,7 @@
       </c>
       <c r="K164" s="33">
         <f t="shared" ca="1" si="10"/>
-        <v>45927</v>
+        <v>45683</v>
       </c>
       <c r="L164" s="45" t="str">
         <f t="shared" si="11"/>
@@ -27361,7 +27361,7 @@
       </c>
       <c r="K165" s="33">
         <f t="shared" ca="1" si="10"/>
-        <v>45818</v>
+        <v>45699</v>
       </c>
       <c r="L165" s="45" t="str">
         <f t="shared" si="11"/>
@@ -27403,7 +27403,7 @@
       </c>
       <c r="K166" s="33">
         <f t="shared" ca="1" si="10"/>
-        <v>45864</v>
+        <v>45937</v>
       </c>
       <c r="L166" s="45" t="str">
         <f t="shared" si="11"/>
@@ -27445,7 +27445,7 @@
       </c>
       <c r="K167" s="33">
         <f t="shared" ca="1" si="10"/>
-        <v>45832</v>
+        <v>45864</v>
       </c>
       <c r="L167" s="45" t="str">
         <f t="shared" si="11"/>
@@ -27487,7 +27487,7 @@
       </c>
       <c r="K168" s="33">
         <f t="shared" ca="1" si="10"/>
-        <v>45790</v>
+        <v>45863</v>
       </c>
       <c r="L168" s="45" t="str">
         <f t="shared" si="11"/>
@@ -27529,7 +27529,7 @@
       </c>
       <c r="K169" s="33">
         <f t="shared" ca="1" si="10"/>
-        <v>45736</v>
+        <v>45750</v>
       </c>
       <c r="L169" s="45" t="str">
         <f t="shared" si="11"/>
@@ -27571,7 +27571,7 @@
       </c>
       <c r="K170" s="33">
         <f t="shared" ca="1" si="10"/>
-        <v>45667</v>
+        <v>45682</v>
       </c>
       <c r="L170" s="45" t="str">
         <f t="shared" si="11"/>
@@ -27613,7 +27613,7 @@
       </c>
       <c r="K171" s="33">
         <f t="shared" ca="1" si="10"/>
-        <v>45843</v>
+        <v>45948</v>
       </c>
       <c r="L171" s="45" t="str">
         <f t="shared" si="11"/>
@@ -27655,7 +27655,7 @@
       </c>
       <c r="K172" s="33">
         <f t="shared" ca="1" si="10"/>
-        <v>45994</v>
+        <v>45770</v>
       </c>
       <c r="L172" s="45" t="str">
         <f t="shared" si="11"/>
@@ -27697,7 +27697,7 @@
       </c>
       <c r="K173" s="33">
         <f t="shared" ca="1" si="10"/>
-        <v>45938</v>
+        <v>45769</v>
       </c>
       <c r="L173" s="45" t="str">
         <f t="shared" si="11"/>
@@ -27739,7 +27739,7 @@
       </c>
       <c r="K174" s="33">
         <f t="shared" ca="1" si="10"/>
-        <v>45981</v>
+        <v>45927</v>
       </c>
       <c r="L174" s="45" t="str">
         <f t="shared" si="11"/>
@@ -27781,7 +27781,7 @@
       </c>
       <c r="K175" s="33">
         <f t="shared" ca="1" si="10"/>
-        <v>45970</v>
+        <v>45976</v>
       </c>
       <c r="L175" s="45" t="str">
         <f t="shared" si="11"/>
@@ -27823,7 +27823,7 @@
       </c>
       <c r="K176" s="33">
         <f t="shared" ca="1" si="10"/>
-        <v>45823</v>
+        <v>45762</v>
       </c>
       <c r="L176" s="45" t="str">
         <f t="shared" si="11"/>
@@ -27865,7 +27865,7 @@
       </c>
       <c r="K177" s="33">
         <f t="shared" ca="1" si="10"/>
-        <v>45842</v>
+        <v>46010</v>
       </c>
       <c r="L177" s="45" t="str">
         <f t="shared" si="11"/>
@@ -27907,7 +27907,7 @@
       </c>
       <c r="K178" s="33">
         <f t="shared" ca="1" si="10"/>
-        <v>45763</v>
+        <v>45975</v>
       </c>
       <c r="L178" s="45" t="str">
         <f t="shared" si="11"/>
@@ -27949,7 +27949,7 @@
       </c>
       <c r="K179" s="33">
         <f t="shared" ca="1" si="10"/>
-        <v>45786</v>
+        <v>45731</v>
       </c>
       <c r="L179" s="45" t="str">
         <f t="shared" si="11"/>
@@ -27991,7 +27991,7 @@
       </c>
       <c r="K180" s="33">
         <f t="shared" ca="1" si="10"/>
-        <v>45976</v>
+        <v>45948</v>
       </c>
       <c r="L180" s="45" t="str">
         <f t="shared" si="11"/>
@@ -28033,7 +28033,7 @@
       </c>
       <c r="K181" s="33">
         <f t="shared" ca="1" si="10"/>
-        <v>45839</v>
+        <v>46010</v>
       </c>
       <c r="L181" s="45" t="str">
         <f t="shared" si="11"/>
@@ -28075,7 +28075,7 @@
       </c>
       <c r="K182" s="33">
         <f t="shared" ca="1" si="10"/>
-        <v>45721</v>
+        <v>45924</v>
       </c>
       <c r="L182" s="45" t="str">
         <f t="shared" si="11"/>
@@ -28117,7 +28117,7 @@
       </c>
       <c r="K183" s="33">
         <f t="shared" ca="1" si="10"/>
-        <v>45708</v>
+        <v>45756</v>
       </c>
       <c r="L183" s="45" t="str">
         <f t="shared" si="11"/>
@@ -28159,7 +28159,7 @@
       </c>
       <c r="K184" s="33">
         <f t="shared" ca="1" si="10"/>
-        <v>45895</v>
+        <v>45773</v>
       </c>
       <c r="L184" s="45" t="str">
         <f t="shared" si="11"/>
@@ -28201,7 +28201,7 @@
       </c>
       <c r="K185" s="33">
         <f t="shared" ca="1" si="10"/>
-        <v>45963</v>
+        <v>45722</v>
       </c>
       <c r="L185" s="45" t="str">
         <f t="shared" si="11"/>
@@ -28243,7 +28243,7 @@
       </c>
       <c r="K186" s="33">
         <f t="shared" ca="1" si="10"/>
-        <v>45787</v>
+        <v>46000</v>
       </c>
       <c r="L186" s="45" t="str">
         <f t="shared" si="11"/>
@@ -28285,7 +28285,7 @@
       </c>
       <c r="K187" s="33">
         <f t="shared" ca="1" si="10"/>
-        <v>45736</v>
+        <v>45980</v>
       </c>
       <c r="L187" s="45" t="str">
         <f t="shared" si="11"/>
@@ -28369,7 +28369,7 @@
       </c>
       <c r="K189" s="33">
         <f t="shared" ca="1" si="10"/>
-        <v>45954</v>
+        <v>45872</v>
       </c>
       <c r="L189" s="45" t="str">
         <f t="shared" si="11"/>
@@ -28411,7 +28411,7 @@
       </c>
       <c r="K190" s="33">
         <f t="shared" ca="1" si="10"/>
-        <v>46013</v>
+        <v>45885</v>
       </c>
       <c r="L190" s="45" t="str">
         <f t="shared" si="11"/>
@@ -28453,7 +28453,7 @@
       </c>
       <c r="K191" s="33">
         <f t="shared" ca="1" si="10"/>
-        <v>45713</v>
+        <v>45941</v>
       </c>
       <c r="L191" s="45" t="str">
         <f t="shared" si="11"/>
@@ -28495,7 +28495,7 @@
       </c>
       <c r="K192" s="33">
         <f t="shared" ca="1" si="10"/>
-        <v>45870</v>
+        <v>45813</v>
       </c>
       <c r="L192" s="45" t="str">
         <f t="shared" si="11"/>
@@ -28537,7 +28537,7 @@
       </c>
       <c r="K193" s="33">
         <f t="shared" ca="1" si="10"/>
-        <v>46011</v>
+        <v>45842</v>
       </c>
       <c r="L193" s="45" t="str">
         <f t="shared" si="11"/>
@@ -28579,7 +28579,7 @@
       </c>
       <c r="K194" s="33">
         <f t="shared" ca="1" si="10"/>
-        <v>45755</v>
+        <v>45893</v>
       </c>
       <c r="L194" s="45" t="str">
         <f t="shared" si="11"/>
@@ -28621,7 +28621,7 @@
       </c>
       <c r="K195" s="33">
         <f t="shared" ref="K195:K258" ca="1" si="14">IF(ROW()&lt;=151,DATE(2024,RANDBETWEEN(1,12),RANDBETWEEN(1,28)),DATE(2025,RANDBETWEEN(1,12),RANDBETWEEN(1,28)))</f>
-        <v>45974</v>
+        <v>45789</v>
       </c>
       <c r="L195" s="45" t="str">
         <f t="shared" ref="L195:L258" si="15">CHOOSE(MOD(ROW()-2,4)+1,"North","South","East","West")</f>
@@ -28663,7 +28663,7 @@
       </c>
       <c r="K196" s="33">
         <f t="shared" ca="1" si="14"/>
-        <v>45981</v>
+        <v>45820</v>
       </c>
       <c r="L196" s="45" t="str">
         <f t="shared" si="15"/>
@@ -28705,7 +28705,7 @@
       </c>
       <c r="K197" s="33">
         <f t="shared" ca="1" si="14"/>
-        <v>45759</v>
+        <v>45853</v>
       </c>
       <c r="L197" s="45" t="str">
         <f t="shared" si="15"/>
@@ -28747,7 +28747,7 @@
       </c>
       <c r="K198" s="33">
         <f t="shared" ca="1" si="14"/>
-        <v>45936</v>
+        <v>45802</v>
       </c>
       <c r="L198" s="45" t="str">
         <f t="shared" si="15"/>
@@ -28789,7 +28789,7 @@
       </c>
       <c r="K199" s="33">
         <f t="shared" ca="1" si="14"/>
-        <v>45820</v>
+        <v>45967</v>
       </c>
       <c r="L199" s="45" t="str">
         <f t="shared" si="15"/>
@@ -28831,7 +28831,7 @@
       </c>
       <c r="K200" s="33">
         <f t="shared" ca="1" si="14"/>
-        <v>45999</v>
+        <v>45678</v>
       </c>
       <c r="L200" s="45" t="str">
         <f t="shared" si="15"/>
@@ -28873,7 +28873,7 @@
       </c>
       <c r="K201" s="33">
         <f t="shared" ca="1" si="14"/>
-        <v>45804</v>
+        <v>45681</v>
       </c>
       <c r="L201" s="45" t="str">
         <f t="shared" si="15"/>
@@ -28915,7 +28915,7 @@
       </c>
       <c r="K202" s="33">
         <f t="shared" ca="1" si="14"/>
-        <v>45871</v>
+        <v>45717</v>
       </c>
       <c r="L202" s="45" t="str">
         <f t="shared" si="15"/>
@@ -28957,7 +28957,7 @@
       </c>
       <c r="K203" s="33">
         <f t="shared" ca="1" si="14"/>
-        <v>45732</v>
+        <v>45779</v>
       </c>
       <c r="L203" s="45" t="str">
         <f t="shared" si="15"/>
@@ -28999,7 +28999,7 @@
       </c>
       <c r="K204" s="33">
         <f t="shared" ca="1" si="14"/>
-        <v>45665</v>
+        <v>45920</v>
       </c>
       <c r="L204" s="45" t="str">
         <f t="shared" si="15"/>
@@ -29041,7 +29041,7 @@
       </c>
       <c r="K205" s="33">
         <f t="shared" ca="1" si="14"/>
-        <v>45720</v>
+        <v>45816</v>
       </c>
       <c r="L205" s="45" t="str">
         <f t="shared" si="15"/>
@@ -29083,7 +29083,7 @@
       </c>
       <c r="K206" s="33">
         <f t="shared" ca="1" si="14"/>
-        <v>45940</v>
+        <v>45708</v>
       </c>
       <c r="L206" s="45" t="str">
         <f t="shared" si="15"/>
@@ -29125,7 +29125,7 @@
       </c>
       <c r="K207" s="33">
         <f t="shared" ca="1" si="14"/>
-        <v>45726</v>
+        <v>45882</v>
       </c>
       <c r="L207" s="45" t="str">
         <f t="shared" si="15"/>
@@ -29167,7 +29167,7 @@
       </c>
       <c r="K208" s="33">
         <f t="shared" ca="1" si="14"/>
-        <v>45700</v>
+        <v>45826</v>
       </c>
       <c r="L208" s="45" t="str">
         <f t="shared" si="15"/>
@@ -29209,7 +29209,7 @@
       </c>
       <c r="K209" s="33">
         <f t="shared" ca="1" si="14"/>
-        <v>45880</v>
+        <v>45673</v>
       </c>
       <c r="L209" s="45" t="str">
         <f t="shared" si="15"/>
@@ -29251,7 +29251,7 @@
       </c>
       <c r="K210" s="33">
         <f t="shared" ca="1" si="14"/>
-        <v>45763</v>
+        <v>45913</v>
       </c>
       <c r="L210" s="45" t="str">
         <f t="shared" si="15"/>
@@ -29293,7 +29293,7 @@
       </c>
       <c r="K211" s="33">
         <f t="shared" ca="1" si="14"/>
-        <v>45981</v>
+        <v>45767</v>
       </c>
       <c r="L211" s="45" t="str">
         <f t="shared" si="15"/>
@@ -29335,7 +29335,7 @@
       </c>
       <c r="K212" s="33">
         <f t="shared" ca="1" si="14"/>
-        <v>45831</v>
+        <v>45705</v>
       </c>
       <c r="L212" s="45" t="str">
         <f t="shared" si="15"/>
@@ -29377,7 +29377,7 @@
       </c>
       <c r="K213" s="33">
         <f t="shared" ca="1" si="14"/>
-        <v>45902</v>
+        <v>46013</v>
       </c>
       <c r="L213" s="45" t="str">
         <f t="shared" si="15"/>
@@ -29419,7 +29419,7 @@
       </c>
       <c r="K214" s="33">
         <f t="shared" ca="1" si="14"/>
-        <v>45973</v>
+        <v>45682</v>
       </c>
       <c r="L214" s="45" t="str">
         <f t="shared" si="15"/>
@@ -29461,7 +29461,7 @@
       </c>
       <c r="K215" s="33">
         <f t="shared" ca="1" si="14"/>
-        <v>45678</v>
+        <v>45907</v>
       </c>
       <c r="L215" s="45" t="str">
         <f t="shared" si="15"/>
@@ -29503,7 +29503,7 @@
       </c>
       <c r="K216" s="33">
         <f t="shared" ca="1" si="14"/>
-        <v>45729</v>
+        <v>45731</v>
       </c>
       <c r="L216" s="45" t="str">
         <f t="shared" si="15"/>
@@ -29545,7 +29545,7 @@
       </c>
       <c r="K217" s="33">
         <f t="shared" ca="1" si="14"/>
-        <v>45857</v>
+        <v>45933</v>
       </c>
       <c r="L217" s="45" t="str">
         <f t="shared" si="15"/>
@@ -29587,7 +29587,7 @@
       </c>
       <c r="K218" s="33">
         <f t="shared" ca="1" si="14"/>
-        <v>45967</v>
+        <v>45955</v>
       </c>
       <c r="L218" s="45" t="str">
         <f t="shared" si="15"/>
@@ -29629,7 +29629,7 @@
       </c>
       <c r="K219" s="33">
         <f t="shared" ca="1" si="14"/>
-        <v>45682</v>
+        <v>45665</v>
       </c>
       <c r="L219" s="45" t="str">
         <f t="shared" si="15"/>
@@ -29671,7 +29671,7 @@
       </c>
       <c r="K220" s="33">
         <f t="shared" ca="1" si="14"/>
-        <v>45980</v>
+        <v>45943</v>
       </c>
       <c r="L220" s="45" t="str">
         <f t="shared" si="15"/>
@@ -29713,7 +29713,7 @@
       </c>
       <c r="K221" s="33">
         <f t="shared" ca="1" si="14"/>
-        <v>45723</v>
+        <v>45774</v>
       </c>
       <c r="L221" s="45" t="str">
         <f t="shared" si="15"/>
@@ -29755,7 +29755,7 @@
       </c>
       <c r="K222" s="33">
         <f t="shared" ca="1" si="14"/>
-        <v>45754</v>
+        <v>45796</v>
       </c>
       <c r="L222" s="45" t="str">
         <f t="shared" si="15"/>
@@ -29797,7 +29797,7 @@
       </c>
       <c r="K223" s="33">
         <f t="shared" ca="1" si="14"/>
-        <v>45730</v>
+        <v>45989</v>
       </c>
       <c r="L223" s="45" t="str">
         <f t="shared" si="15"/>
@@ -29839,7 +29839,7 @@
       </c>
       <c r="K224" s="33">
         <f t="shared" ca="1" si="14"/>
-        <v>45685</v>
+        <v>45785</v>
       </c>
       <c r="L224" s="45" t="str">
         <f t="shared" si="15"/>
@@ -29881,7 +29881,7 @@
       </c>
       <c r="K225" s="33">
         <f t="shared" ca="1" si="14"/>
-        <v>45859</v>
+        <v>45659</v>
       </c>
       <c r="L225" s="45" t="str">
         <f t="shared" si="15"/>
@@ -29923,7 +29923,7 @@
       </c>
       <c r="K226" s="33">
         <f t="shared" ca="1" si="14"/>
-        <v>45915</v>
+        <v>45952</v>
       </c>
       <c r="L226" s="45" t="str">
         <f t="shared" si="15"/>
@@ -29965,7 +29965,7 @@
       </c>
       <c r="K227" s="33">
         <f t="shared" ca="1" si="14"/>
-        <v>45709</v>
+        <v>45992</v>
       </c>
       <c r="L227" s="45" t="str">
         <f t="shared" si="15"/>
@@ -30007,7 +30007,7 @@
       </c>
       <c r="K228" s="33">
         <f t="shared" ca="1" si="14"/>
-        <v>45701</v>
+        <v>45924</v>
       </c>
       <c r="L228" s="45" t="str">
         <f t="shared" si="15"/>
@@ -30049,7 +30049,7 @@
       </c>
       <c r="K229" s="33">
         <f t="shared" ca="1" si="14"/>
-        <v>45877</v>
+        <v>45695</v>
       </c>
       <c r="L229" s="45" t="str">
         <f t="shared" si="15"/>
@@ -30091,7 +30091,7 @@
       </c>
       <c r="K230" s="33">
         <f t="shared" ca="1" si="14"/>
-        <v>46012</v>
+        <v>45844</v>
       </c>
       <c r="L230" s="45" t="str">
         <f t="shared" si="15"/>
@@ -30133,7 +30133,7 @@
       </c>
       <c r="K231" s="33">
         <f t="shared" ca="1" si="14"/>
-        <v>45997</v>
+        <v>45812</v>
       </c>
       <c r="L231" s="45" t="str">
         <f t="shared" si="15"/>
@@ -30175,7 +30175,7 @@
       </c>
       <c r="K232" s="33">
         <f t="shared" ca="1" si="14"/>
-        <v>45936</v>
+        <v>45724</v>
       </c>
       <c r="L232" s="45" t="str">
         <f t="shared" si="15"/>
@@ -30217,7 +30217,7 @@
       </c>
       <c r="K233" s="33">
         <f t="shared" ca="1" si="14"/>
-        <v>45793</v>
+        <v>45835</v>
       </c>
       <c r="L233" s="45" t="str">
         <f t="shared" si="15"/>
@@ -30259,7 +30259,7 @@
       </c>
       <c r="K234" s="33">
         <f t="shared" ca="1" si="14"/>
-        <v>46004</v>
+        <v>45683</v>
       </c>
       <c r="L234" s="45" t="str">
         <f t="shared" si="15"/>
@@ -30301,7 +30301,7 @@
       </c>
       <c r="K235" s="33">
         <f t="shared" ca="1" si="14"/>
-        <v>45873</v>
+        <v>45802</v>
       </c>
       <c r="L235" s="45" t="str">
         <f t="shared" si="15"/>
@@ -30343,7 +30343,7 @@
       </c>
       <c r="K236" s="33">
         <f t="shared" ca="1" si="14"/>
-        <v>45755</v>
+        <v>45883</v>
       </c>
       <c r="L236" s="45" t="str">
         <f t="shared" si="15"/>
@@ -30385,7 +30385,7 @@
       </c>
       <c r="K237" s="33">
         <f t="shared" ca="1" si="14"/>
-        <v>45784</v>
+        <v>45790</v>
       </c>
       <c r="L237" s="45" t="str">
         <f t="shared" si="15"/>
@@ -30427,7 +30427,7 @@
       </c>
       <c r="K238" s="33">
         <f t="shared" ca="1" si="14"/>
-        <v>45974</v>
+        <v>45873</v>
       </c>
       <c r="L238" s="45" t="str">
         <f t="shared" si="15"/>
@@ -30469,7 +30469,7 @@
       </c>
       <c r="K239" s="33">
         <f t="shared" ca="1" si="14"/>
-        <v>45719</v>
+        <v>45882</v>
       </c>
       <c r="L239" s="45" t="str">
         <f t="shared" si="15"/>
@@ -30511,7 +30511,7 @@
       </c>
       <c r="K240" s="33">
         <f t="shared" ca="1" si="14"/>
-        <v>45810</v>
+        <v>45724</v>
       </c>
       <c r="L240" s="45" t="str">
         <f t="shared" si="15"/>
@@ -30553,7 +30553,7 @@
       </c>
       <c r="K241" s="33">
         <f t="shared" ca="1" si="14"/>
-        <v>45890</v>
+        <v>45840</v>
       </c>
       <c r="L241" s="45" t="str">
         <f t="shared" si="15"/>
@@ -30595,7 +30595,7 @@
       </c>
       <c r="K242" s="33">
         <f t="shared" ca="1" si="14"/>
-        <v>45848</v>
+        <v>45943</v>
       </c>
       <c r="L242" s="45" t="str">
         <f t="shared" si="15"/>
@@ -30637,7 +30637,7 @@
       </c>
       <c r="K243" s="33">
         <f t="shared" ca="1" si="14"/>
-        <v>45666</v>
+        <v>45754</v>
       </c>
       <c r="L243" s="45" t="str">
         <f t="shared" si="15"/>
@@ -30679,7 +30679,7 @@
       </c>
       <c r="K244" s="33">
         <f t="shared" ca="1" si="14"/>
-        <v>45943</v>
+        <v>46005</v>
       </c>
       <c r="L244" s="45" t="str">
         <f t="shared" si="15"/>
@@ -30721,7 +30721,7 @@
       </c>
       <c r="K245" s="33">
         <f t="shared" ca="1" si="14"/>
-        <v>45703</v>
+        <v>45725</v>
       </c>
       <c r="L245" s="45" t="str">
         <f t="shared" si="15"/>
@@ -30763,7 +30763,7 @@
       </c>
       <c r="K246" s="33">
         <f t="shared" ca="1" si="14"/>
-        <v>45699</v>
+        <v>45828</v>
       </c>
       <c r="L246" s="45" t="str">
         <f t="shared" si="15"/>
@@ -30805,7 +30805,7 @@
       </c>
       <c r="K247" s="33">
         <f t="shared" ca="1" si="14"/>
-        <v>45884</v>
+        <v>45836</v>
       </c>
       <c r="L247" s="45" t="str">
         <f t="shared" si="15"/>
@@ -30847,7 +30847,7 @@
       </c>
       <c r="K248" s="33">
         <f t="shared" ca="1" si="14"/>
-        <v>45896</v>
+        <v>46005</v>
       </c>
       <c r="L248" s="45" t="str">
         <f t="shared" si="15"/>
@@ -30889,7 +30889,7 @@
       </c>
       <c r="K249" s="33">
         <f t="shared" ca="1" si="14"/>
-        <v>45685</v>
+        <v>45692</v>
       </c>
       <c r="L249" s="45" t="str">
         <f t="shared" si="15"/>
@@ -30931,7 +30931,7 @@
       </c>
       <c r="K250" s="33">
         <f t="shared" ca="1" si="14"/>
-        <v>45715</v>
+        <v>45737</v>
       </c>
       <c r="L250" s="45" t="str">
         <f t="shared" si="15"/>
@@ -30973,7 +30973,7 @@
       </c>
       <c r="K251" s="33">
         <f t="shared" ca="1" si="14"/>
-        <v>45921</v>
+        <v>45945</v>
       </c>
       <c r="L251" s="45" t="str">
         <f t="shared" si="15"/>
@@ -31015,7 +31015,7 @@
       </c>
       <c r="K252" s="33">
         <f t="shared" ca="1" si="14"/>
-        <v>45721</v>
+        <v>45859</v>
       </c>
       <c r="L252" s="45" t="str">
         <f t="shared" si="15"/>
@@ -31057,7 +31057,7 @@
       </c>
       <c r="K253" s="33">
         <f t="shared" ca="1" si="14"/>
-        <v>45795</v>
+        <v>45927</v>
       </c>
       <c r="L253" s="45" t="str">
         <f t="shared" si="15"/>
@@ -31099,7 +31099,7 @@
       </c>
       <c r="K254" s="33">
         <f t="shared" ca="1" si="14"/>
-        <v>45663</v>
+        <v>45742</v>
       </c>
       <c r="L254" s="45" t="str">
         <f t="shared" si="15"/>
@@ -31141,7 +31141,7 @@
       </c>
       <c r="K255" s="33">
         <f t="shared" ca="1" si="14"/>
-        <v>45874</v>
+        <v>45885</v>
       </c>
       <c r="L255" s="45" t="str">
         <f t="shared" si="15"/>
@@ -31183,7 +31183,7 @@
       </c>
       <c r="K256" s="33">
         <f t="shared" ca="1" si="14"/>
-        <v>45738</v>
+        <v>45995</v>
       </c>
       <c r="L256" s="45" t="str">
         <f t="shared" si="15"/>
@@ -31225,7 +31225,7 @@
       </c>
       <c r="K257" s="33">
         <f t="shared" ca="1" si="14"/>
-        <v>45876</v>
+        <v>45669</v>
       </c>
       <c r="L257" s="45" t="str">
         <f t="shared" si="15"/>
@@ -31267,7 +31267,7 @@
       </c>
       <c r="K258" s="33">
         <f t="shared" ca="1" si="14"/>
-        <v>45698</v>
+        <v>45891</v>
       </c>
       <c r="L258" s="45" t="str">
         <f t="shared" si="15"/>
@@ -31309,7 +31309,7 @@
       </c>
       <c r="K259" s="33">
         <f t="shared" ref="K259:K302" ca="1" si="18">IF(ROW()&lt;=151,DATE(2024,RANDBETWEEN(1,12),RANDBETWEEN(1,28)),DATE(2025,RANDBETWEEN(1,12),RANDBETWEEN(1,28)))</f>
-        <v>45877</v>
+        <v>45712</v>
       </c>
       <c r="L259" s="45" t="str">
         <f t="shared" ref="L259:L302" si="19">CHOOSE(MOD(ROW()-2,4)+1,"North","South","East","West")</f>
@@ -31351,7 +31351,7 @@
       </c>
       <c r="K260" s="33">
         <f t="shared" ca="1" si="18"/>
-        <v>45850</v>
+        <v>45835</v>
       </c>
       <c r="L260" s="45" t="str">
         <f t="shared" si="19"/>
@@ -31393,7 +31393,7 @@
       </c>
       <c r="K261" s="33">
         <f t="shared" ca="1" si="18"/>
-        <v>45934</v>
+        <v>45833</v>
       </c>
       <c r="L261" s="45" t="str">
         <f t="shared" si="19"/>
@@ -31435,7 +31435,7 @@
       </c>
       <c r="K262" s="33">
         <f t="shared" ca="1" si="18"/>
-        <v>45891</v>
+        <v>45771</v>
       </c>
       <c r="L262" s="45" t="str">
         <f t="shared" si="19"/>
@@ -31477,7 +31477,7 @@
       </c>
       <c r="K263" s="33">
         <f t="shared" ca="1" si="18"/>
-        <v>45879</v>
+        <v>45697</v>
       </c>
       <c r="L263" s="45" t="str">
         <f t="shared" si="19"/>
@@ -31519,7 +31519,7 @@
       </c>
       <c r="K264" s="33">
         <f t="shared" ca="1" si="18"/>
-        <v>45813</v>
+        <v>45727</v>
       </c>
       <c r="L264" s="45" t="str">
         <f t="shared" si="19"/>
@@ -31561,7 +31561,7 @@
       </c>
       <c r="K265" s="33">
         <f t="shared" ca="1" si="18"/>
-        <v>45766</v>
+        <v>45740</v>
       </c>
       <c r="L265" s="45" t="str">
         <f t="shared" si="19"/>
@@ -31603,7 +31603,7 @@
       </c>
       <c r="K266" s="33">
         <f t="shared" ca="1" si="18"/>
-        <v>45743</v>
+        <v>45921</v>
       </c>
       <c r="L266" s="45" t="str">
         <f t="shared" si="19"/>
@@ -31645,7 +31645,7 @@
       </c>
       <c r="K267" s="33">
         <f t="shared" ca="1" si="18"/>
-        <v>45771</v>
+        <v>45787</v>
       </c>
       <c r="L267" s="45" t="str">
         <f t="shared" si="19"/>
@@ -31687,7 +31687,7 @@
       </c>
       <c r="K268" s="33">
         <f t="shared" ca="1" si="18"/>
-        <v>45748</v>
+        <v>45883</v>
       </c>
       <c r="L268" s="45" t="str">
         <f t="shared" si="19"/>
@@ -31729,7 +31729,7 @@
       </c>
       <c r="K269" s="33">
         <f t="shared" ca="1" si="18"/>
-        <v>45989</v>
+        <v>45998</v>
       </c>
       <c r="L269" s="45" t="str">
         <f t="shared" si="19"/>
@@ -31771,7 +31771,7 @@
       </c>
       <c r="K270" s="33">
         <f t="shared" ca="1" si="18"/>
-        <v>45924</v>
+        <v>45791</v>
       </c>
       <c r="L270" s="45" t="str">
         <f t="shared" si="19"/>
@@ -31813,7 +31813,7 @@
       </c>
       <c r="K271" s="33">
         <f t="shared" ca="1" si="18"/>
-        <v>45934</v>
+        <v>46019</v>
       </c>
       <c r="L271" s="45" t="str">
         <f t="shared" si="19"/>
@@ -31855,7 +31855,7 @@
       </c>
       <c r="K272" s="33">
         <f t="shared" ca="1" si="18"/>
-        <v>45815</v>
+        <v>45727</v>
       </c>
       <c r="L272" s="45" t="str">
         <f t="shared" si="19"/>
@@ -31897,7 +31897,7 @@
       </c>
       <c r="K273" s="33">
         <f t="shared" ca="1" si="18"/>
-        <v>45740</v>
+        <v>45726</v>
       </c>
       <c r="L273" s="45" t="str">
         <f t="shared" si="19"/>
@@ -31939,7 +31939,7 @@
       </c>
       <c r="K274" s="33">
         <f t="shared" ca="1" si="18"/>
-        <v>45843</v>
+        <v>45795</v>
       </c>
       <c r="L274" s="45" t="str">
         <f t="shared" si="19"/>
@@ -31981,7 +31981,7 @@
       </c>
       <c r="K275" s="33">
         <f t="shared" ca="1" si="18"/>
-        <v>45895</v>
+        <v>45847</v>
       </c>
       <c r="L275" s="45" t="str">
         <f t="shared" si="19"/>
@@ -32023,7 +32023,7 @@
       </c>
       <c r="K276" s="33">
         <f t="shared" ca="1" si="18"/>
-        <v>45762</v>
+        <v>45931</v>
       </c>
       <c r="L276" s="45" t="str">
         <f t="shared" si="19"/>
@@ -32065,7 +32065,7 @@
       </c>
       <c r="K277" s="33">
         <f t="shared" ca="1" si="18"/>
-        <v>45690</v>
+        <v>45749</v>
       </c>
       <c r="L277" s="45" t="str">
         <f t="shared" si="19"/>
@@ -32107,7 +32107,7 @@
       </c>
       <c r="K278" s="33">
         <f t="shared" ca="1" si="18"/>
-        <v>46001</v>
+        <v>45985</v>
       </c>
       <c r="L278" s="45" t="str">
         <f t="shared" si="19"/>
@@ -32149,7 +32149,7 @@
       </c>
       <c r="K279" s="33">
         <f t="shared" ca="1" si="18"/>
-        <v>45716</v>
+        <v>45903</v>
       </c>
       <c r="L279" s="45" t="str">
         <f t="shared" si="19"/>
@@ -32191,7 +32191,7 @@
       </c>
       <c r="K280" s="33">
         <f t="shared" ca="1" si="18"/>
-        <v>45943</v>
+        <v>45992</v>
       </c>
       <c r="L280" s="45" t="str">
         <f t="shared" si="19"/>
@@ -32233,7 +32233,7 @@
       </c>
       <c r="K281" s="33">
         <f t="shared" ca="1" si="18"/>
-        <v>45858</v>
+        <v>45918</v>
       </c>
       <c r="L281" s="45" t="str">
         <f t="shared" si="19"/>
@@ -32275,7 +32275,7 @@
       </c>
       <c r="K282" s="33">
         <f t="shared" ca="1" si="18"/>
-        <v>45672</v>
+        <v>45689</v>
       </c>
       <c r="L282" s="45" t="str">
         <f t="shared" si="19"/>
@@ -32317,7 +32317,7 @@
       </c>
       <c r="K283" s="33">
         <f t="shared" ca="1" si="18"/>
-        <v>45748</v>
+        <v>45915</v>
       </c>
       <c r="L283" s="45" t="str">
         <f t="shared" si="19"/>
@@ -32359,7 +32359,7 @@
       </c>
       <c r="K284" s="33">
         <f t="shared" ca="1" si="18"/>
-        <v>45963</v>
+        <v>46012</v>
       </c>
       <c r="L284" s="45" t="str">
         <f t="shared" si="19"/>
@@ -32401,7 +32401,7 @@
       </c>
       <c r="K285" s="33">
         <f t="shared" ca="1" si="18"/>
-        <v>45805</v>
+        <v>45847</v>
       </c>
       <c r="L285" s="45" t="str">
         <f t="shared" si="19"/>
@@ -32443,7 +32443,7 @@
       </c>
       <c r="K286" s="33">
         <f t="shared" ca="1" si="18"/>
-        <v>45757</v>
+        <v>45824</v>
       </c>
       <c r="L286" s="45" t="str">
         <f t="shared" si="19"/>
@@ -32485,7 +32485,7 @@
       </c>
       <c r="K287" s="33">
         <f t="shared" ca="1" si="18"/>
-        <v>45816</v>
+        <v>45742</v>
       </c>
       <c r="L287" s="45" t="str">
         <f t="shared" si="19"/>
@@ -32527,7 +32527,7 @@
       </c>
       <c r="K288" s="33">
         <f t="shared" ca="1" si="18"/>
-        <v>45682</v>
+        <v>45903</v>
       </c>
       <c r="L288" s="45" t="str">
         <f t="shared" si="19"/>
@@ -32569,7 +32569,7 @@
       </c>
       <c r="K289" s="33">
         <f t="shared" ca="1" si="18"/>
-        <v>45720</v>
+        <v>45744</v>
       </c>
       <c r="L289" s="45" t="str">
         <f t="shared" si="19"/>
@@ -32611,7 +32611,7 @@
       </c>
       <c r="K290" s="33">
         <f t="shared" ca="1" si="18"/>
-        <v>45664</v>
+        <v>45870</v>
       </c>
       <c r="L290" s="45" t="str">
         <f t="shared" si="19"/>
@@ -32653,7 +32653,7 @@
       </c>
       <c r="K291" s="33">
         <f t="shared" ca="1" si="18"/>
-        <v>46013</v>
+        <v>45720</v>
       </c>
       <c r="L291" s="45" t="str">
         <f t="shared" si="19"/>
@@ -32695,7 +32695,7 @@
       </c>
       <c r="K292" s="33">
         <f t="shared" ca="1" si="18"/>
-        <v>45674</v>
+        <v>45916</v>
       </c>
       <c r="L292" s="45" t="str">
         <f t="shared" si="19"/>
@@ -32737,7 +32737,7 @@
       </c>
       <c r="K293" s="33">
         <f t="shared" ca="1" si="18"/>
-        <v>45944</v>
+        <v>45736</v>
       </c>
       <c r="L293" s="45" t="str">
         <f t="shared" si="19"/>
@@ -32779,7 +32779,7 @@
       </c>
       <c r="K294" s="33">
         <f t="shared" ca="1" si="18"/>
-        <v>45706</v>
+        <v>45957</v>
       </c>
       <c r="L294" s="45" t="str">
         <f t="shared" si="19"/>
@@ -32821,7 +32821,7 @@
       </c>
       <c r="K295" s="33">
         <f t="shared" ca="1" si="18"/>
-        <v>45927</v>
+        <v>45957</v>
       </c>
       <c r="L295" s="45" t="str">
         <f t="shared" si="19"/>
@@ -32863,7 +32863,7 @@
       </c>
       <c r="K296" s="33">
         <f t="shared" ca="1" si="18"/>
-        <v>45863</v>
+        <v>45864</v>
       </c>
       <c r="L296" s="45" t="str">
         <f t="shared" si="19"/>
@@ -32905,7 +32905,7 @@
       </c>
       <c r="K297" s="33">
         <f t="shared" ca="1" si="18"/>
-        <v>45948</v>
+        <v>45805</v>
       </c>
       <c r="L297" s="45" t="str">
         <f t="shared" si="19"/>
@@ -32947,7 +32947,7 @@
       </c>
       <c r="K298" s="33">
         <f t="shared" ca="1" si="18"/>
-        <v>45697</v>
+        <v>45965</v>
       </c>
       <c r="L298" s="45" t="str">
         <f t="shared" si="19"/>
@@ -32989,7 +32989,7 @@
       </c>
       <c r="K299" s="33">
         <f t="shared" ca="1" si="18"/>
-        <v>45682</v>
+        <v>45802</v>
       </c>
       <c r="L299" s="45" t="str">
         <f t="shared" si="19"/>
@@ -33031,7 +33031,7 @@
       </c>
       <c r="K300" s="33">
         <f t="shared" ca="1" si="18"/>
-        <v>45815</v>
+        <v>45661</v>
       </c>
       <c r="L300" s="45" t="str">
         <f t="shared" si="19"/>
@@ -33073,7 +33073,7 @@
       </c>
       <c r="K301" s="33">
         <f t="shared" ca="1" si="18"/>
-        <v>45933</v>
+        <v>45902</v>
       </c>
       <c r="L301" s="45" t="str">
         <f t="shared" si="19"/>
@@ -33115,7 +33115,7 @@
       </c>
       <c r="K302" s="56">
         <f t="shared" ca="1" si="18"/>
-        <v>45671</v>
+        <v>45829</v>
       </c>
       <c r="L302" s="57" t="str">
         <f t="shared" si="19"/>
